--- a/Output Files GPT-OSS 20B/LLM-Parameterized_Reference_Scoring_results_run_04.xlsx
+++ b/Output Files GPT-OSS 20B/LLM-Parameterized_Reference_Scoring_results_run_04.xlsx
@@ -38279,7 +38279,7 @@
         <v>3</v>
       </c>
       <c r="AD407" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="408">
@@ -39680,7 +39680,7 @@
         <v>0.77</v>
       </c>
       <c r="AA422" t="n">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
       <c r="AB422" t="n">
         <v>0.5</v>
@@ -39689,7 +39689,7 @@
         <v>1</v>
       </c>
       <c r="AD422" t="n">
-        <v>0.6814999999999999</v>
+        <v>0.6995</v>
       </c>
     </row>
     <row r="423">
@@ -39774,7 +39774,7 @@
         <v>0.58</v>
       </c>
       <c r="AA423" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="AB423" t="n">
         <v>0.52</v>
@@ -39783,7 +39783,7 @@
         <v>2</v>
       </c>
       <c r="AD423" t="n">
-        <v>0.581</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="424">
@@ -39868,7 +39868,7 @@
         <v>0.38</v>
       </c>
       <c r="AA424" t="n">
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
       <c r="AB424" t="n">
         <v>0.67</v>
@@ -39877,7 +39877,7 @@
         <v>3</v>
       </c>
       <c r="AD424" t="n">
-        <v>0.4465</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="425">
@@ -40347,7 +40347,7 @@
         <v>2</v>
       </c>
       <c r="AD429" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="430">
@@ -40432,7 +40432,7 @@
         <v>0.58</v>
       </c>
       <c r="AA430" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="AB430" t="n">
         <v>0.52</v>
@@ -40441,7 +40441,7 @@
         <v>3</v>
       </c>
       <c r="AD430" t="n">
-        <v>0.597</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="431">
@@ -40629,7 +40629,7 @@
         <v>2</v>
       </c>
       <c r="AD432" t="n">
-        <v>0.7129999999999999</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="433">
@@ -40808,7 +40808,7 @@
         <v>0.13</v>
       </c>
       <c r="AA434" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AB434" t="n">
         <v>0.46</v>
@@ -40817,7 +40817,7 @@
         <v>1</v>
       </c>
       <c r="AD434" t="n">
-        <v>0.2865</v>
+        <v>0.2885</v>
       </c>
     </row>
     <row r="435">
@@ -40902,7 +40902,7 @@
         <v>0</v>
       </c>
       <c r="AA435" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB435" t="n">
         <v>0.67</v>
@@ -40911,7 +40911,7 @@
         <v>2</v>
       </c>
       <c r="AD435" t="n">
-        <v>0.2605000000000001</v>
+        <v>0.2785</v>
       </c>
     </row>
     <row r="436">
@@ -40996,7 +40996,7 @@
         <v>0</v>
       </c>
       <c r="AA436" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="AB436" t="n">
         <v>0.48</v>
@@ -41005,7 +41005,7 @@
         <v>3</v>
       </c>
       <c r="AD436" t="n">
-        <v>0.162</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="437">
@@ -41090,7 +41090,7 @@
         <v>0</v>
       </c>
       <c r="AA437" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="AB437" t="n">
         <v>0.57</v>
@@ -41099,7 +41099,7 @@
         <v>1</v>
       </c>
       <c r="AD437" t="n">
-        <v>0.2865</v>
+        <v>0.3005</v>
       </c>
     </row>
     <row r="438">
@@ -41184,7 +41184,7 @@
         <v>0</v>
       </c>
       <c r="AA438" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="AB438" t="n">
         <v>0.52</v>
@@ -41193,7 +41193,7 @@
         <v>2</v>
       </c>
       <c r="AD438" t="n">
-        <v>0.168</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="439">
@@ -41278,7 +41278,7 @@
         <v>0</v>
       </c>
       <c r="AA439" t="n">
-        <v>0.06</v>
+        <v>0.21</v>
       </c>
       <c r="AB439" t="n">
         <v>0.4</v>
@@ -41287,7 +41287,7 @@
         <v>3</v>
       </c>
       <c r="AD439" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="440">
@@ -41381,7 +41381,7 @@
         <v>1</v>
       </c>
       <c r="AD440" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="441">
@@ -41466,7 +41466,7 @@
         <v>0.51</v>
       </c>
       <c r="AA441" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB441" t="n">
         <v>0.57</v>
@@ -41475,7 +41475,7 @@
         <v>2</v>
       </c>
       <c r="AD441" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="442">
@@ -41560,7 +41560,7 @@
         <v>0.19</v>
       </c>
       <c r="AA442" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB442" t="n">
         <v>0.52</v>
@@ -41569,7 +41569,7 @@
         <v>3</v>
       </c>
       <c r="AD442" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="443">
@@ -41757,7 +41757,7 @@
         <v>2</v>
       </c>
       <c r="AD444" t="n">
-        <v>0.6839999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="445">
@@ -42030,7 +42030,7 @@
         <v>0</v>
       </c>
       <c r="AA447" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB447" t="n">
         <v>0.57</v>
@@ -42039,7 +42039,7 @@
         <v>2</v>
       </c>
       <c r="AD447" t="n">
-        <v>0.2675</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="448">
@@ -42124,7 +42124,7 @@
         <v>0</v>
       </c>
       <c r="AA448" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB448" t="n">
         <v>0.52</v>
@@ -42133,7 +42133,7 @@
         <v>3</v>
       </c>
       <c r="AD448" t="n">
-        <v>0.188</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="449">
@@ -42500,7 +42500,7 @@
         <v>0.38</v>
       </c>
       <c r="AA452" t="n">
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
       <c r="AB452" t="n">
         <v>0.67</v>
@@ -42509,7 +42509,7 @@
         <v>1</v>
       </c>
       <c r="AD452" t="n">
-        <v>0.4465</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="453">
@@ -42594,7 +42594,7 @@
         <v>0.19</v>
       </c>
       <c r="AA453" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AB453" t="n">
         <v>0.52</v>
@@ -42603,7 +42603,7 @@
         <v>2</v>
       </c>
       <c r="AD453" t="n">
-        <v>0.2375</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="454">
@@ -42688,7 +42688,7 @@
         <v>0</v>
       </c>
       <c r="AA454" t="n">
-        <v>0.06</v>
+        <v>0.36</v>
       </c>
       <c r="AB454" t="n">
         <v>0.4</v>
@@ -42697,7 +42697,7 @@
         <v>3</v>
       </c>
       <c r="AD454" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="455">
@@ -42885,7 +42885,7 @@
         <v>1</v>
       </c>
       <c r="AD456" t="n">
-        <v>0.7599999999999999</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="457">
@@ -43355,7 +43355,7 @@
         <v>3</v>
       </c>
       <c r="AD461" t="n">
-        <v>0.7084999999999999</v>
+        <v>0.7085</v>
       </c>
     </row>
     <row r="462">
@@ -43449,7 +43449,7 @@
         <v>2</v>
       </c>
       <c r="AD462" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="463">
@@ -43825,7 +43825,7 @@
         <v>3</v>
       </c>
       <c r="AD466" t="n">
-        <v>0.7589999999999999</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="467">
@@ -43910,7 +43910,7 @@
         <v>0.64</v>
       </c>
       <c r="AA467" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AB467" t="n">
         <v>0.46</v>
@@ -43919,7 +43919,7 @@
         <v>1</v>
       </c>
       <c r="AD467" t="n">
-        <v>0.6240000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="468">
@@ -44004,7 +44004,7 @@
         <v>0.38</v>
       </c>
       <c r="AA468" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB468" t="n">
         <v>0.67</v>
@@ -44013,7 +44013,7 @@
         <v>2</v>
       </c>
       <c r="AD468" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="469">
@@ -44098,7 +44098,7 @@
         <v>0.19</v>
       </c>
       <c r="AA469" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB469" t="n">
         <v>0.52</v>
@@ -44107,7 +44107,7 @@
         <v>3</v>
       </c>
       <c r="AD469" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="470">
@@ -44295,7 +44295,7 @@
         <v>1</v>
       </c>
       <c r="AD471" t="n">
-        <v>0.8815000000000001</v>
+        <v>0.8815</v>
       </c>
     </row>
     <row r="472">
@@ -44389,7 +44389,7 @@
         <v>3</v>
       </c>
       <c r="AD472" t="n">
-        <v>0.7989999999999999</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="473">
@@ -44765,7 +44765,7 @@
         <v>1</v>
       </c>
       <c r="AD476" t="n">
-        <v>0.6044999999999999</v>
+        <v>0.6045</v>
       </c>
     </row>
     <row r="477">
@@ -45047,7 +45047,7 @@
         <v>1</v>
       </c>
       <c r="AD479" t="n">
-        <v>0.5279999999999999</v>
+        <v>0.528</v>
       </c>
     </row>
     <row r="480">
@@ -45226,7 +45226,7 @@
         <v>0</v>
       </c>
       <c r="AA481" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB481" t="n">
         <v>0.57</v>
@@ -45235,7 +45235,7 @@
         <v>3</v>
       </c>
       <c r="AD481" t="n">
-        <v>0.2675</v>
+        <v>0.2795</v>
       </c>
     </row>
     <row r="482">
@@ -45329,7 +45329,7 @@
         <v>1</v>
       </c>
       <c r="AD482" t="n">
-        <v>0.7589999999999999</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="483">
@@ -45508,7 +45508,7 @@
         <v>0.19</v>
       </c>
       <c r="AA484" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="AB484" t="n">
         <v>0.52</v>
@@ -45517,7 +45517,7 @@
         <v>3</v>
       </c>
       <c r="AD484" t="n">
-        <v>0.3235</v>
+        <v>0.3375</v>
       </c>
     </row>
     <row r="485">
@@ -45611,7 +45611,7 @@
         <v>1</v>
       </c>
       <c r="AD485" t="n">
-        <v>0.7555000000000001</v>
+        <v>0.7554999999999999</v>
       </c>
     </row>
     <row r="486">
@@ -45893,7 +45893,7 @@
         <v>1</v>
       </c>
       <c r="AD488" t="n">
-        <v>0.8064999999999999</v>
+        <v>0.8065</v>
       </c>
     </row>
     <row r="489">
@@ -45978,7 +45978,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA489" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="AB489" t="n">
         <v>0.67</v>
@@ -45987,7 +45987,7 @@
         <v>2</v>
       </c>
       <c r="AD489" t="n">
-        <v>0.7010000000000001</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="490">
@@ -46072,7 +46072,7 @@
         <v>0.38</v>
       </c>
       <c r="AA490" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AB490" t="n">
         <v>0.32</v>
@@ -46081,7 +46081,7 @@
         <v>3</v>
       </c>
       <c r="AD490" t="n">
-        <v>0.289</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="491">
@@ -46166,16 +46166,16 @@
         <v>1</v>
       </c>
       <c r="AA491" t="n">
-        <v>0.03</v>
+        <v>0.18</v>
       </c>
       <c r="AB491" t="n">
         <v>0.15</v>
       </c>
       <c r="AC491" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD491" t="n">
-        <v>0.6784999999999999</v>
+        <v>0.7085</v>
       </c>
     </row>
     <row r="492">
@@ -46260,16 +46260,16 @@
         <v>0.71</v>
       </c>
       <c r="AA492" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AB492" t="n">
         <v>0.64</v>
       </c>
       <c r="AC492" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD492" t="n">
-        <v>0.6825</v>
+        <v>0.6985</v>
       </c>
     </row>
     <row r="493">
@@ -46354,7 +46354,7 @@
         <v>0.26</v>
       </c>
       <c r="AA493" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="AB493" t="n">
         <v>0.57</v>
@@ -46363,7 +46363,7 @@
         <v>3</v>
       </c>
       <c r="AD493" t="n">
-        <v>0.3855000000000001</v>
+        <v>0.3995</v>
       </c>
     </row>
     <row r="494">
@@ -46551,7 +46551,7 @@
         <v>2</v>
       </c>
       <c r="AD495" t="n">
-        <v>0.8379999999999999</v>
+        <v>0.838</v>
       </c>
     </row>
     <row r="496">
@@ -46927,7 +46927,7 @@
         <v>3</v>
       </c>
       <c r="AD499" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="500">
@@ -47294,7 +47294,7 @@
         <v>0.83</v>
       </c>
       <c r="AA503" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="AB503" t="n">
         <v>0.35</v>
@@ -47303,7 +47303,7 @@
         <v>1</v>
       </c>
       <c r="AD503" t="n">
-        <v>0.717</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="504">
@@ -47388,7 +47388,7 @@
         <v>0.64</v>
       </c>
       <c r="AA504" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AB504" t="n">
         <v>0.76</v>
@@ -47397,7 +47397,7 @@
         <v>2</v>
       </c>
       <c r="AD504" t="n">
-        <v>0.711</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="505">
@@ -47482,7 +47482,7 @@
         <v>0.38</v>
       </c>
       <c r="AA505" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AB505" t="n">
         <v>0.93</v>
@@ -47491,7 +47491,7 @@
         <v>3</v>
       </c>
       <c r="AD505" t="n">
-        <v>0.5735000000000001</v>
+        <v>0.5875</v>
       </c>
     </row>
     <row r="506">
@@ -47952,7 +47952,7 @@
         <v>0.64</v>
       </c>
       <c r="AA510" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AB510" t="n">
         <v>0.46</v>
@@ -47961,7 +47961,7 @@
         <v>2</v>
       </c>
       <c r="AD510" t="n">
-        <v>0.6519999999999999</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="511">
@@ -48046,7 +48046,7 @@
         <v>0.38</v>
       </c>
       <c r="AA511" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="AB511" t="n">
         <v>0.67</v>
@@ -48055,7 +48055,7 @@
         <v>3</v>
       </c>
       <c r="AD511" t="n">
-        <v>0.4965000000000001</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="512">
@@ -48140,7 +48140,7 @@
         <v>0.64</v>
       </c>
       <c r="AA512" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB512" t="n">
         <v>0.46</v>
@@ -48149,7 +48149,7 @@
         <v>1</v>
       </c>
       <c r="AD512" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="513">
@@ -48234,7 +48234,7 @@
         <v>0.51</v>
       </c>
       <c r="AA513" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB513" t="n">
         <v>0.57</v>
@@ -48243,7 +48243,7 @@
         <v>2</v>
       </c>
       <c r="AD513" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="514">
@@ -48328,7 +48328,7 @@
         <v>0.38</v>
       </c>
       <c r="AA514" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="AB514" t="n">
         <v>0.67</v>
@@ -48337,7 +48337,7 @@
         <v>3</v>
       </c>
       <c r="AD514" t="n">
-        <v>0.5065000000000001</v>
+        <v>0.5185</v>
       </c>
     </row>
     <row r="515">
@@ -48516,7 +48516,7 @@
         <v>0.51</v>
       </c>
       <c r="AA516" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="AB516" t="n">
         <v>0.57</v>
@@ -48525,7 +48525,7 @@
         <v>2</v>
       </c>
       <c r="AD516" t="n">
-        <v>0.5950000000000001</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="517">
@@ -48610,7 +48610,7 @@
         <v>0.38</v>
       </c>
       <c r="AA517" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="AB517" t="n">
         <v>0.67</v>
@@ -48619,7 +48619,7 @@
         <v>3</v>
       </c>
       <c r="AD517" t="n">
-        <v>0.4995000000000001</v>
+        <v>0.5135</v>
       </c>
     </row>
     <row r="518">
@@ -48704,7 +48704,7 @@
         <v>0.64</v>
       </c>
       <c r="AA518" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AB518" t="n">
         <v>0.46</v>
@@ -48713,7 +48713,7 @@
         <v>1</v>
       </c>
       <c r="AD518" t="n">
-        <v>0.6779999999999999</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="519">
@@ -48798,7 +48798,7 @@
         <v>0.51</v>
       </c>
       <c r="AA519" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AB519" t="n">
         <v>0.57</v>
@@ -48807,7 +48807,7 @@
         <v>2</v>
       </c>
       <c r="AD519" t="n">
-        <v>0.6090000000000001</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="520">
@@ -48892,7 +48892,7 @@
         <v>0.38</v>
       </c>
       <c r="AA520" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="AB520" t="n">
         <v>0.67</v>
@@ -48901,7 +48901,7 @@
         <v>3</v>
       </c>
       <c r="AD520" t="n">
-        <v>0.5185000000000001</v>
+        <v>0.5265</v>
       </c>
     </row>
     <row r="521">
@@ -48986,7 +48986,7 @@
         <v>0.85</v>
       </c>
       <c r="AA521" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB521" t="n">
         <v>0.46</v>
@@ -48995,7 +48995,7 @@
         <v>1</v>
       </c>
       <c r="AD521" t="n">
-        <v>0.7985</v>
+        <v>0.8005</v>
       </c>
     </row>
     <row r="522">
@@ -49080,7 +49080,7 @@
         <v>0.77</v>
       </c>
       <c r="AA522" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB522" t="n">
         <v>0.57</v>
@@ -49089,7 +49089,7 @@
         <v>2</v>
       </c>
       <c r="AD522" t="n">
-        <v>0.768</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="523">
@@ -49174,7 +49174,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA523" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="AB523" t="n">
         <v>0.67</v>
@@ -49183,7 +49183,7 @@
         <v>3</v>
       </c>
       <c r="AD523" t="n">
-        <v>0.7050000000000001</v>
+        <v>0.717</v>
       </c>
     </row>
     <row r="524">
@@ -49362,7 +49362,7 @@
         <v>0.51</v>
       </c>
       <c r="AA525" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AB525" t="n">
         <v>0.57</v>
@@ -49371,7 +49371,7 @@
         <v>2</v>
       </c>
       <c r="AD525" t="n">
-        <v>0.6080000000000001</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="526">
@@ -49456,7 +49456,7 @@
         <v>0.38</v>
       </c>
       <c r="AA526" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="AB526" t="n">
         <v>0.67</v>
@@ -49465,7 +49465,7 @@
         <v>3</v>
       </c>
       <c r="AD526" t="n">
-        <v>0.5155000000000001</v>
+        <v>0.5255</v>
       </c>
     </row>
     <row r="527">
@@ -49653,7 +49653,7 @@
         <v>2</v>
       </c>
       <c r="AD528" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="529">
@@ -50217,7 +50217,7 @@
         <v>2</v>
       </c>
       <c r="AD534" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="535">
@@ -50499,7 +50499,7 @@
         <v>1</v>
       </c>
       <c r="AD537" t="n">
-        <v>0.8059999999999999</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="538">
@@ -50687,7 +50687,7 @@
         <v>1</v>
       </c>
       <c r="AD539" t="n">
-        <v>0.7344999999999999</v>
+        <v>0.7345</v>
       </c>
     </row>
     <row r="540">
@@ -51148,7 +51148,7 @@
         <v>0.51</v>
       </c>
       <c r="AA544" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB544" t="n">
         <v>0.57</v>
@@ -51157,7 +51157,7 @@
         <v>3</v>
       </c>
       <c r="AD544" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="545">
@@ -51251,7 +51251,7 @@
         <v>3</v>
       </c>
       <c r="AD545" t="n">
-        <v>0.6764999999999999</v>
+        <v>0.6765</v>
       </c>
     </row>
     <row r="546">
@@ -51345,7 +51345,7 @@
         <v>1</v>
       </c>
       <c r="AD546" t="n">
-        <v>0.8270000000000001</v>
+        <v>0.827</v>
       </c>
     </row>
     <row r="547">
@@ -51533,7 +51533,7 @@
         <v>1</v>
       </c>
       <c r="AD548" t="n">
-        <v>0.7829999999999999</v>
+        <v>0.783</v>
       </c>
     </row>
     <row r="549">
@@ -51627,7 +51627,7 @@
         <v>2</v>
       </c>
       <c r="AD549" t="n">
-        <v>0.5395000000000001</v>
+        <v>0.5395</v>
       </c>
     </row>
     <row r="550">
@@ -52285,7 +52285,7 @@
         <v>3</v>
       </c>
       <c r="AD556" t="n">
-        <v>0.5455000000000001</v>
+        <v>0.5455</v>
       </c>
     </row>
     <row r="557">
@@ -52379,7 +52379,7 @@
         <v>1</v>
       </c>
       <c r="AD557" t="n">
-        <v>0.6769999999999999</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="558">
@@ -52464,7 +52464,7 @@
         <v>0.64</v>
       </c>
       <c r="AA558" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB558" t="n">
         <v>0.46</v>
@@ -52473,7 +52473,7 @@
         <v>2</v>
       </c>
       <c r="AD558" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="559">
@@ -52558,7 +52558,7 @@
         <v>0.51</v>
       </c>
       <c r="AA559" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB559" t="n">
         <v>0.57</v>
@@ -52567,7 +52567,7 @@
         <v>3</v>
       </c>
       <c r="AD559" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="560">
@@ -52746,7 +52746,7 @@
         <v>0.62</v>
       </c>
       <c r="AA561" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AB561" t="n">
         <v>0.57</v>
@@ -52755,7 +52755,7 @@
         <v>2</v>
       </c>
       <c r="AD561" t="n">
-        <v>0.6735000000000001</v>
+        <v>0.6815</v>
       </c>
     </row>
     <row r="562">
@@ -52840,7 +52840,7 @@
         <v>0.51</v>
       </c>
       <c r="AA562" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="AB562" t="n">
         <v>0.67</v>
@@ -52849,7 +52849,7 @@
         <v>3</v>
       </c>
       <c r="AD562" t="n">
-        <v>0.5940000000000001</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="563">
@@ -53131,7 +53131,7 @@
         <v>3</v>
       </c>
       <c r="AD565" t="n">
-        <v>0.7509999999999999</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="566">
@@ -53225,7 +53225,7 @@
         <v>3</v>
       </c>
       <c r="AD566" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="567">
@@ -53413,7 +53413,7 @@
         <v>1</v>
       </c>
       <c r="AD568" t="n">
-        <v>0.8624999999999999</v>
+        <v>0.8625</v>
       </c>
     </row>
     <row r="569">
@@ -53695,7 +53695,7 @@
         <v>3</v>
       </c>
       <c r="AD571" t="n">
-        <v>0.7149999999999999</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="572">
@@ -53789,7 +53789,7 @@
         <v>1</v>
       </c>
       <c r="AD572" t="n">
-        <v>0.7649999999999999</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="573">
@@ -53977,7 +53977,7 @@
         <v>3</v>
       </c>
       <c r="AD574" t="n">
-        <v>0.7069999999999999</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="575">
@@ -54071,7 +54071,7 @@
         <v>1</v>
       </c>
       <c r="AD575" t="n">
-        <v>0.7589999999999999</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="576">
@@ -54353,7 +54353,7 @@
         <v>3</v>
       </c>
       <c r="AD578" t="n">
-        <v>0.7994999999999999</v>
+        <v>0.7995</v>
       </c>
     </row>
     <row r="579">
@@ -54447,7 +54447,7 @@
         <v>1</v>
       </c>
       <c r="AD579" t="n">
-        <v>0.8059999999999999</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="580">
@@ -54541,7 +54541,7 @@
         <v>2</v>
       </c>
       <c r="AD580" t="n">
-        <v>0.8029999999999999</v>
+        <v>0.803</v>
       </c>
     </row>
     <row r="581">
@@ -54635,7 +54635,7 @@
         <v>3</v>
       </c>
       <c r="AD581" t="n">
-        <v>0.8074999999999999</v>
+        <v>0.8075</v>
       </c>
     </row>
     <row r="582">
@@ -54729,7 +54729,7 @@
         <v>1</v>
       </c>
       <c r="AD582" t="n">
-        <v>0.8170000000000001</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="583">
@@ -54823,7 +54823,7 @@
         <v>2</v>
       </c>
       <c r="AD583" t="n">
-        <v>0.8139999999999998</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="584">
@@ -55105,7 +55105,7 @@
         <v>3</v>
       </c>
       <c r="AD586" t="n">
-        <v>0.6859999999999999</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
   </sheetData>
